--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Pethikuppam_13.433004_80.120213.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Pethikuppam_13.433004_80.120213.xlsx
@@ -1070,6 +1070,11 @@
           <t>146</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C1A1, 2C1A2, 2C1B, 2C1C, 2C2, 2C3</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1077,6 +1082,11 @@
           <t>147</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1084,6 +1094,11 @@
           <t>148</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A1A, 2A1B, 2A1C, 2A1D, 2A2A, 2A2B, 2B1A1, 2B1A2, 2B1B, 2B2, 3, 4A, 4B, 4C1, 4C2A, 4C2B</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1091,6 +1106,11 @@
           <t>149</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1, 2A1A1, 2A1A1B, 2A1B, 2A2A, 2A2B, 2A2C, 2B, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1098,6 +1118,11 @@
           <t>15</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1105,6 +1130,11 @@
           <t>150</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15A, 15B, 16, 17, 18, 19, 1A1, 1A2, 1A3, 1A4, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 3A, 3B1, 3B2A1A, 3B2B, 3C1A, 3C2, 4A1, 4A2A1, 4A2B, 4B1A, 4B1B, 4B2A1, 4B2B, 5A1, 5A2A, 5A2B, 5B10, 5B11, 5B12, 5B13, 5B14, 5B15, 5B16, 5B17, 5B18, 5B19, 5B1A1, 5B2, 5B20, 5B21, 5B22, 5B23, 5B24, 5B3, 5B4, 5B5, 5B6, 5B7, 5B8, 5B9, 5D, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1112,6 +1142,11 @@
           <t>151</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1119,6 +1154,11 @@
           <t>152A</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1126,6 +1166,11 @@
           <t>152B</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1133,6 +1178,11 @@
           <t>153</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1140,6 +1190,11 @@
           <t>154/A</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1147,6 +1202,11 @@
           <t>154/B</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1154,6 +1214,11 @@
           <t>155/A</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1161,6 +1226,11 @@
           <t>155/B</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1168,6 +1238,11 @@
           <t>155/C</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1175,6 +1250,11 @@
           <t>156</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B1, 1B2, 1B3, 1B4, 1B5, 1C, 1D, 2</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1182,6 +1262,11 @@
           <t>157</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>10, 11, 1A1A, 1A1B, 1A2, 1B1A1, 1B1B, 1B2A1A, 1B2A1B, 1B2B, 1B3, 1B4, 2A1, 2A2, 2A3, 2B1, 2B2, 2C1, 2C2, 2C2A, 2D1A1, 2D2, 3A, 3B, 5, 6, 7, 8A, 8B1, 8B2, 9</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1189,6 +1274,11 @@
           <t>158</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D1, 1D2, 2A1, 2A2, 2A3, 2B, 3A1A, 3A1B, 3A1C, 3A1D, 3A1E, 3A1F, 3A1G, 3A1H, 3A1I, 3A1J, 3A1K, 3A1L, 3A1M1, 3A1M2, 3A1N, 3A2A, 3A2B, 3A2C, 3A2D, 3A2E, 3A2F, 3A2G, 3A2H, 3A2I, 3A2J, 3A3A, 3A3B, 3A3C, 3A4A, 3A4B1, 3A4B2, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1196,6 +1286,11 @@
           <t>159/A</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1203,6 +1298,11 @@
           <t>159/B</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1210,6 +1310,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1, 2, 3A1, 3A2, 3B1, 3B2, 3C, 3D</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1217,6 +1322,11 @@
           <t>160</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1224,6 +1334,11 @@
           <t>161</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 15, 2A1A1A1, 2A1A1B, 2A1A1C1, 2A1A2A, 2A1A2B, 2A1A2C, 2A1B, 2A2A, 2A2B, 2A3A1, 2A3B, 2B1A1A1, 2B1A1B, 2B1A2A1, 2B1A2A2, 2B1A2B, 2B1A3, 2B1A4, 2B1A5, 2B1B, 2B2A1A, 2B2A2, 2B2B, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1231,6 +1346,11 @@
           <t>162</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>12, 1A1A1A1, 1A1A1B1, 1A1A1B2, 1A1A2A1A1, 1A1A2A1B, 1A1A2A2, 1A1A2A3A, 1A1A2A3B, 1A1A2A4, 1A1B, 1A1B1A1B, 1A1B1A2, 1A1B1B, 1A1B2A, 1A1C1A1, 1A1C1B1, 1A1C1B2, 1A1C1C1, 1A1C1C2, 1A1C2, 1A2, 1B1, 1B1A1A1A1A, 2A, 2B, 36, 37, 38, 3A1A, 3A1B, 3A2, 3B1, 3B2, 4A, 4B, 5A, 5A1, 5A2A, 5A2B, 5B1, 5B2, 6A, 6B1, 6B2, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1238,6 +1358,11 @@
           <t>163</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>10, 11, 12A1, 12B, 13A, 13B, 14, 15, 16, 17, 18, 19, 1A1A1, 1A1A2, 1A1B, 1A2A1A1, 1A2A2, 1A2B1, 1A2B2A1, 1A2B2A10, 1A2B2A11A1, 1A2B2A11B, 1A2B2A12A, 1A2B2A13A, 1A2B2A14, 1A2B2A15, 1A2B2A16, 1A2B2A17A, 1A2B2A18, 1A2B2A19, 1A2B2A2, 1A2B2A20, 1A2B2A21A, 1A2B2A22A, 1A2B2A22B, 1A2B2A23, 1A2B2A23BB, 1A2B2A24A1, 1A2B2A25A1, 1A2B2A25A2, 1A2B2A25A3, 1A2B2A25A4, 1A2B2A25B, 1A2B2A26, 1A2B2A27, 1A2B2A28, 1A2B2A3, 1A2B2A30A1, 1A2B2A31, 1A2B2A4, 1A2B2A5A1, 1A2B2A5A2, 1A2B2A5B1, 1A2B2A5C1, 1A2B2A7, 1A2B2A8, 1A2B2A9, 1A2B2B1A1, 1A2B2B2, 1A2B2B6A1, 1A2B2B6A2, 1A2C1A, 1A2C1B, 1A2C2, 1A2D10, 1A2D1A, 1A2D2, 1A2D8, 1A2D9, 1A2E, 1B1A, 1B1B, 1B1C, 1B1D, 1B1E, 1B1F, 1B1G, 1B1H, 1B1I, 1B2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A1, 2A1B, 2A2, 2A3, 2A4, 2A5, 2A6, 2A7A, 2A7B, 2A7C, 2B, 30, 31, 32, 33, 34, 35, 36A, 36B1, 36B2, 37, 38, 39, 3A, 3B, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49A, 49B, 5, 50, 51A1A, 51A2, 51B, 52A, 52B, 53, 54, 55, 56, 57, 58, 59, 6, 60, 61, 62, 63, 64A, 64B, 65, 66, 67, 68, 69, 7, 70, 71, 72, 73, 74, 75, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1245,6 +1370,11 @@
           <t>164</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2A1, 2A2, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1252,6 +1382,11 @@
           <t>165</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3A1, 1A3A2, 1A3B, 1B, 2A1A, 2A1B, 2A2A1A, 2A2A2, 2A2A3, 2A2A4, 2A2A5, 2A2A6, 2A2A7, 2A2A8, 2A2A9, 2A2B1, 2A2B2, 2A2B3, 2A2B4, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1259,6 +1394,11 @@
           <t>166</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2A1A, 2A2A, 2A2B, 2B1A1, 2B1A2, 2B1B, 2B2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1266,6 +1406,11 @@
           <t>167</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1A4, 1A5, 1B1A, 1B1B, 1B2, 1B3A, 1B3B, 2A1, 2A2, 2A3, 2A4, 2B, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1273,6 +1418,11 @@
           <t>168</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2A1A, 2A1B, 2A2A, 2B, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1280,6 +1430,11 @@
           <t>169</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1C, 1D, 1E1, 1E2, 1F1, 1F2, 2A, 2B1A1, 2B1A2, 2B2, 3A, 3B1, 3B2, 3B3, 4, 5A1, 5A2, 5B, 5C, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1287,6 +1442,11 @@
           <t>17</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A, 3B1, 3B2, 3B3, 4A, 4B, 5A, 5B, 5C, 5D, 6A, 6B, 6C, 6D, 7, 8A, 8B</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1294,6 +1454,11 @@
           <t>170</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2, 3, 4A, 4B, 5, 6A, 6B, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1301,6 +1466,11 @@
           <t>171</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1308,6 +1478,11 @@
           <t>172</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1315,6 +1490,11 @@
           <t>173</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1A1, 1B1A1, 1B1A2A, 1B1A2B, 1B1A2C, 1B1B, 1B2, 2A1A1, 2A1A2, 2A1B, 2A2A1A, 2A2A2, 2A2B1, 2A2B2, 2A2B3, 2A3, 2A4, 2B, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1322,6 +1502,11 @@
           <t>174</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1A1, 1B1A1A1, 1B2, 1B3, 1B4, 1B5, 1B6, 1B7, 1B8, 20, 21, 22, 23, 24, 25, 26, 2A1A, 2A1A2, 2A1B, 2A2, 2A3, 2B, 2C, 3A1, 3A2, 3B1, 3B2, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1329,6 +1514,11 @@
           <t>175</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2A1, 2A2, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1336,6 +1526,11 @@
           <t>176</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1, 10, 2A1A, 2A1B, 2A2, 2B, 3A, 3B, 4A1A1A1, 4A1A1B, 4A1A2A1, 4A1A2B, 4A1A3A1, 4A1A3B, 4A1B1, 4A1B2, 4A2A, 4A2B, 4A3A, 4A3B, 4B, 4C, 5A1, 5A2, 5A3A, 5A3A2, 5B, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1343,6 +1538,11 @@
           <t>177</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1350,6 +1550,11 @@
           <t>178</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1A, 1B, 3</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1357,6 +1562,11 @@
           <t>179</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13A, 13B, 14A, 14B, 15, 15A, 15B, 16, 17, 18A, 18B, 19, 1A, 1B1, 1B2A, 1B2B, 1B2C, 1B2D, 1B2E, 1B3A, 1B3B, 20, 21, 23, 24, 25, 26, 27, 28, 29, 2A1A, 2A1B, 2A1C, 2A2A, 2A2B1A, 2A2C1A, 2A2D, 2A2E, 2A2F, 2A2G, 2A2H, 2A2I, 2A2J, 2A2K, 2A2L, 2A3A, 2A3B1, 2A3B2, 2B, 3A1A, 3A1B, 3A2A, 3A2B, 3A3A, 3A3B, 3B, 4A, 4B1A1A1, 4B1A1B, 4B1A1C, 4B1A2, 4B1B, 4B1C, 4B1D1A1, 4B1D1A2, 4B1D1B, 4B1D2A, 4B1D2B, 4B2, 5A1, 5A2, 5B, 6, 7A, 7B1A1, 7B1A2, 7B1B1A, 7B1B1B, 7B1B2, 7B2A, 7B2B, 7B3, 8A, 8B1A, 8B1B, 8B1C1, 8B1C2, 8B1D1, 8B1D2, 8B1E, 8B2A, 8B2B, 8B2C, 8B2D, 8B2E, 8B2F, 8B3, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1364,6 +1574,11 @@
           <t>18</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>10A1, 10A2, 10A3, 10B, 11A, 11B, 12A, 12B, 13, 14, 15A1, 15A2, 15B, 16A1, 16A2A, 16A2B, 16A3A, 16A3B, 16B, 17, 18, 19, 1A1, 1A2A1, 1A2A2, 1A2B, 1A2C, 1B1A1, 1B1B, 1B2, 1B3, 1B4, 2, 20, 21A, 21B, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 3A, 3B, 3C, 4A1, 4A2, 4A3, 4B, 4C, 4C2, 4D, 4E1A, 4E1B, 4E1C, 4E1D, 4E1E, 4E1F, 4E1G, 4E2, 4E3, 4F1, 4F2A1, 4F2A2, 4F2B, 4G1, 4G2, 4H1, 4H2, 4H3A, 4H3B, 4I1A, 4I1B, 4I2A, 4I2B, 4J1, 4J2, 4K, 4L1A, 4L1A2, 4L1B, 4L2, 4M1, 4M2, 4N1A, 4N2, 4O1A, 4O1B, 4O2, 4P4, 4P5, 4Q1A, 4Q1B, 4Q1C, 4Q2, 4R, 5A1, 5A2, 5A3, 5A4A1, 5A4A2, 5A4A3, 5A4A4, 5A4A5, 5A4B, 5A5, 5A6A, 5A6B, 5A6C, 5A6D, 5A6E2, 5A6E3, 5A6E4, 5A6F, 5AE1A1, 5B, 5C1, 5C2, 6A, 6B1A, 6B1B, 6B1C1, 6B1C2, 6B1C3, 6B2, 7A1, 7A2, 7A3, 7B, 7C1, 7C2A, 7C2B, 7D1, 7D2, 7D3, 7E1, 7E2, 7E3, 7E4A, 7E4B, 8A, 8B, 8C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1371,6 +1586,11 @@
           <t>180</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1378,6 +1598,11 @@
           <t>181</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1385,6 +1610,11 @@
           <t>182</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3A, 1A3B, 1A3C, 1B1, 2, 3A1, 3A2, 3B1A1, 3B1B, 3B1C, 3B2, 3C, 4</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1392,6 +1622,11 @@
           <t>183</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3A, 3B1A, 3B1B, 3B2, 4A, 4B1, 4B2, 4B3A, 4B3B, 4B4, 4B5, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1399,6 +1634,11 @@
           <t>184</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B2, 2C1, 2C2</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1406,6 +1646,11 @@
           <t>185</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 2B1, 2B2, 2B3</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1413,6 +1658,11 @@
           <t>186</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1420,6 +1670,11 @@
           <t>187</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 2A, 2B, 3A1, 3A2, 3B, 3C, 4A, 4B, 5A, 5B</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1427,6 +1682,11 @@
           <t>188</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1B3, 2A1, 2A2, 2B1, 2B2, 2B3, 2B4, 2B5, 3A, 3B, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1434,6 +1694,11 @@
           <t>189</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3A, 1B, 2A, 2B, 3A, 3B, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1441,6 +1706,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1448,6 +1718,11 @@
           <t>190</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1455,6 +1730,11 @@
           <t>191</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1462,6 +1742,11 @@
           <t>192</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1469,6 +1754,11 @@
           <t>193</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4A, 4B, 4C, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1476,6 +1766,11 @@
           <t>194</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B, 2C, 2D, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1483,6 +1778,11 @@
           <t>195/A</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1490,6 +1790,11 @@
           <t>195/B</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1497,6 +1802,11 @@
           <t>196/A</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1504,6 +1814,11 @@
           <t>196/B</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1511,6 +1826,11 @@
           <t>197/A</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1518,6 +1838,11 @@
           <t>197/B</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1525,6 +1850,11 @@
           <t>198/A</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1532,6 +1862,11 @@
           <t>198/B</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1539,6 +1874,11 @@
           <t>199/A</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1546,6 +1886,11 @@
           <t>199/B</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1553,6 +1898,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B1, 2B2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1560,6 +1910,11 @@
           <t>20</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -1567,6 +1922,11 @@
           <t>200/A</t>
         </is>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -1574,11 +1934,21 @@
           <t>200/B</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
           <t>201</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1A1A1A, 1A1A2, 1A2, 1A3, 1B1A, 1B1B1, 1B2, 1B3, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 1J, 1K, 1L, 2A, 2B, 2C, 2D, 2E, 2F1A, 2F1B1, 2F1B2, 2F2, 2F3, 2G1, 2G1A1, 2G1A2, 2G1A3, 2G2, 2H1, 2H2, 2H3, 3, 4, 5</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Pethikuppam_13.433004_80.120213.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Pethikuppam_13.433004_80.120213.xlsx
@@ -1958,6 +1958,11 @@
           <t>202</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1, 2A1A, 2A1B, 2A1C, 2A2A, 2A2B, 2A2C1A, 2A2C1B, 2A2C2, 2A2D1, 2A2D2, 2A2D3, 2A3, 2B, 3A, 3B1, 3B2, 4A1, 4A2, 4B, 5</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1965,6 +1970,11 @@
           <t>203</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13A, 13B, 14, 15, 16A, 16B, 17, 18, 19, 1A1, 1A2, 1B1A, 1B1B, 1B2A, 1B2B, 1B3, 1C11A, 1C1B, 1C1C, 1C1D, 1C2A1, 1C2B1A, 1C2B2A, 1C2B2B, 1C2B2C, 1C2B2D, 1C2B2E, 1C2B2F, 2, 20, 21, 22, 23, 24, 25, 26, 27, 3A1A, 3A2, 3B1, 3B2, 4A, 4A1A, 4A2, 4B1A1A, 4B1B, 4B2A, 4B2B, 4B3, 5A1, 5A2, 5A3A1, 5A3B, 5A3C, 5A3D, 5A3E, 5B1A, 5B1B, 5B2, 6A1, 6A2, 6B1, 6B2, 7A1, 7A2, 7B1, 7B2A, 7B2B, 8A1, 8A2, 8A3, 8B1, 8B2A, 8B2B, 8B2C, 9</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1972,6 +1982,11 @@
           <t>204</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1A1, 1A2A1, 1A2B, 1B1A1A1A, 1B1A2, 1B1B, 1B1C, 1B2, 1C1A1, 1C1A2, 1C1A3, 1C1A4, 1C1B, 1C1C, 1C2, 2A, 2B, 3, 3A, 3B1A1A1, 3B1B, 3B2, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1979,6 +1994,11 @@
           <t>205</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>10A, 10B, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 1C1, 1C2, 1D1, 1D2A, 1D2B, 20A, 20B, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A1A1A, 2A1A1A2, 2A1A1B, 2A1A2, 2A1A3, 2A1B, 2A2, 2B2, 2B3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 45, 46, 47, 47A, 48, 49, 4B, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 5A2, 5A3, 5B3A, 5B3B, 5B3C, 5B3D1, 5B3D2, 5B4A, 5B4B1, 5B5A1A, 5B6A, 5B6B1A, 5B7A1A, 5B7A2, 5B7A3, 5B7A4A, 5B7B1, 5B7B2, 5B7B3, 5B8A, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 6B1, 7, 70, 71, 72, 73, 74, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1986,6 +2006,11 @@
           <t>206</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1993,6 +2018,11 @@
           <t>207</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2000,6 +2030,11 @@
           <t>208</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 12C, 12D, 12E, 12F, 13, 14, 15, 16, 17, 18A, 18B, 2, 3A1, 3A2, 3B1, 3B2, 4A1A1A, 4A1A2, 4A1A3, 4A1A4, 4A1B, 4A2A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2007,6 +2042,11 @@
           <t>209</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2014,6 +2054,11 @@
           <t>21</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2021,6 +2066,11 @@
           <t>210</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2028,6 +2078,11 @@
           <t>211</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I, 2A, 2B1A1, 2B1A2, 2B1B, 2B2A, 2B2B, 2B2C, 3A1, 3A2, 3A3, 3A4, 3A5, 3A6, 3B1, 3B2A, 3B2B, 3B3A, 3B3B, 4A, 4B, 4C, 4D, 4E, 4F, 4G, 4H, 5A1A, 5A2A, 5A2B, 5B1, 5B2, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2035,6 +2090,11 @@
           <t>212</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2042,6 +2102,11 @@
           <t>213</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1A4, 1A5A, 1A5B, 1A6, 1A7, 1A8, 1A9, 1B1, 1B2, 2A1A, 2A1B1, 2A2, 2B, 3A, 3B, 3C, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2049,6 +2114,11 @@
           <t>214</t>
         </is>
       </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2056,6 +2126,11 @@
           <t>215</t>
         </is>
       </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2063,6 +2138,11 @@
           <t>216</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13A, 13B, 14A1, 14B, 15A1A1, 15A2, 15B, 16, 17A1AA, 17A2, 17A3, 17B1, 17B2, 18A, 18B1, 18B2A, 18C1A1, 18C1A2, 18C1B, 18C1C, 18C2, 18D, 18E, 18F, 18G1A, 18G2, 19A, 19B, 19C1, 19C2, 1A, 1B1A, 1B1B, 1B2A1A, 1B2B, 1B3A16, 1B3A1A1, 1B3A1B, 1B3A2, 1B3A3A, 1B3A3B, 1B3A3C1, 1B3A3C2, 1B3A4, 1B3A5A, 1B3A5B, 1B3A6A, 1B3A7, 1B3B, 1B4, 1B5A1, 1B5B, 1B5C, 1C1, 1C2, 1C3, 1C4A1, 1C4A2, 1C4B, 1D1A, 1D1B, 1D1C, 1D1D, 1D1E, 1D1F, 1D1G, 1D2, 1E1, 1E2, 1E3, 1E4, 1E5, 1E8, 1F1A, 1F1B, 1F2, 1F3, 1F4, 1F5, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2070,6 +2150,11 @@
           <t>217</t>
         </is>
       </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2077,6 +2162,11 @@
           <t>218</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1A1, 1A2A1, 1A2B, 1A2C, 1A3, 1B, 2A1A, 2A1B, 2A2A, 2A2B, 2A3, 2A4, 2B2, 2C, 4A1A, 4A1B, 4A2A, 4A2B, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2084,6 +2174,11 @@
           <t>219</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>10, 1A10, 1A1A1A1A, 1A1I, 1A2, 1A3, 1A4, 1A5, 1A6, 1A7, 1A8, 1A9, 1B, 1C, 1D, 1E, 1F1, 1F2, 1G, 1H, 2A1A1, 2A2, 2B1, 2B2, 3A1, 3A2, 3A3, 3B, 4A, 4B1, 4B2, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2091,6 +2186,11 @@
           <t>22</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2098,6 +2198,11 @@
           <t>220</t>
         </is>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1A1A1A, 1A2, 1B, 2, 3, 4, 5, 6A, 6B, 6C, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2105,6 +2210,11 @@
           <t>221</t>
         </is>
       </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1A1A1A1, 1A1A1B, 1A2, 1A3, 1B, 1C, 1D, 1E, 1F, 1G, 2A1, 2A2, 2B, 3A1A, 3A1B, 3A2, 3B, 4, 5, 5A, 5B, 5C, 5D, 6A, 6B, 6C, 6D, 7A1A1, 7A1B, 7A1C, 7A2, 7A3, 7B, 7C, 7D, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2112,6 +2222,11 @@
           <t>222</t>
         </is>
       </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1A1A, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2119,6 +2234,11 @@
           <t>223</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 3A1, 3A2, 3B, 3C, 3D, 4</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2126,6 +2246,11 @@
           <t>224</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 12, 1A1, 1A2, 1A3A, 1A3B, 1A4, 1A5A1, 1A5A2, 1A5B, 1B1B, 1B2A, 1B2B, 1B3, 1B4, 1B5, 1B6, 1B7, 1B8, 1C1, 1C2, 2A1A1A, 2A1A1B1, 2A1A1B2, 2A1A2A, 2A1A2B, 2A1B, 2A1C, 2A1D, 3, 4, 5, 6, 7, 8, 9, B1A1A</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2133,6 +2258,11 @@
           <t>225</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 1A1A, 1A1B, 1A2A, 1B1, 1C1, 1C2A, 1C2A1, 1C2A2A, 1C2B1A1, 1C2B2, 1D1A, 1D1B, 1D2, 1E1, 1E2, 2A1A, 2A2, 2A3, 2A4, 2A5, 2A6, 2B1, 2B2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2140,6 +2270,11 @@
           <t>226</t>
         </is>
       </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2147,11 +2282,21 @@
           <t>227</t>
         </is>
       </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1A, 1A1B, 1A2, 1B, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 5, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 6, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 7, 70, 71, 72A1, 72A2, 72B, 73, 74, 75, 76, 77A, 77B, 78, 79, 8, 80, 81A1, 81B, 81C, 81D, 81E, 82A, 82B, 82C, 83, 84, 85, 86, 9</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
           <t>228</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1A1, 1A1B, 1A2, 1A3A1A1A, 1A3B, 1A4, 1A5, 1B, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A1A, 2A1B, 2A1C, 2A1D, 2A2, 2A3A, 2A3B, 2A4, 2A5, 2B, 3A1A, 3A1B, 3A1C, 3A2, 3A3B, 3A4, 3A5, 3A6, 3A7, 3B, 4A1, 4A2, 4B1, 4B2, 4C1, 4C2, 4C3, 5A1A1A, 5A2, 5B, 5C, 5D, 6, 7, 8, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Pethikuppam_13.433004_80.120213.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Pethikuppam_13.433004_80.120213.xlsx
@@ -2306,6 +2306,11 @@
           <t>229</t>
         </is>
       </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2A3, 2A4, 2A5A1, 2A5B, 2B1A1A1, 2B1A1B, 2B1B, 2B1C, 2B1D1, 2B2, 2B3, 2B4, 2C, 3, 4, 5, 6A, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2313,6 +2318,11 @@
           <t>23</t>
         </is>
       </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2320,6 +2330,11 @@
           <t>230</t>
         </is>
       </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1, 10, 100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 11, 110, 111, 112, 113, 114, 115, 116, 117, 118, 119, 12, 120, 121, 123, 124, 125, 126, 127, 128, 129, 13, 130, 131, 132, 133, 134, 135, 136, 137, 138, 139, 14, 140, 141, 142, 143, 144, 145, 146, 147, 148, 149, 15, 151, 152, 153, 154, 155, 156, 157, 158, 159, 16, 160, 161, 162, 163, 164A, 164B, 164C, 164D, 164E, 164F, 164G, 165A, 165B, 166, 167, 168, 169, 17, 170, 171, 172, 173A, 173B, 174, 175, 176, 178, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A1A1, 2A1A1A2, 2A1A1A3, 2A1A1A4, 2A1A1A5, 2A1A1B, 2A1A1C, 2A1A1D, 2A1A2, 2A1B1, 2A1B2, 2A1C1, 2A1D, 2A2, 2A3, 2A4, 2AC1, 2B1A, 2B1B, 2B2, 2B3, 30, 31, 32, 33A, 33B, 34A, 34B, 35, 36, 37, 38, 39, 3A1, 3A2, 3B1A, 3B1B, 3B2, 40, 41, 42B, 43, 44, 45, 46, 47A, 47B, 48, 49A1A1, 49A1A1A2, 49A1A1A3, 49A1A2, 49A1A3, 49A1B, 49A2, 49B1, 49B2, 49C, 4A1A1A1A, 4A1A2, 4B1, 4B2, 4C1, 4D, 4E1A1A1, 4E1B, 4E1C1, 4E2, 50, 51A, 51B, 52, 53, 54, 55, 56, 57, 58, 59, 5A1A, 5A1B, 5A1C1, 5A1C2, 5A2, 5B, 5C, 60, 61, 62, 63, 64, 65, 66, 67, 68A, 68B, 69, 6A, 6B, 7, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79A1, 79A2, 79A3, 79A4, 79A5, 79B, 8, 80A1, 80A2, 80B, 80C, 81, 82, 83A, 83B, 84, 85, 86, 87, 88, 89A, 89B, 9, 90, 91, 92, 93, 94, 95, 96, 97, 98, 99</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2327,6 +2342,11 @@
           <t>231</t>
         </is>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>10, 11, 12A1, 12A2, 12A3, 12B, 13, 14, 15A, 15B, 16, 17, 18, 19, 1A, 1A1A1A2A, 1A1A1A3A, 1A1A1B, 1A1A21A, 1A1A3, 1A1B, 1A1C, 1A2A, 1A2B, 1A3, 1A4, 1A5, 1A6, 1A7, 1B1, 1B2, 1B3A, 1B3B, 20, 21, 23, 24, 2A, 2A1A1A, 2A1A1B, 2A1A1C, 2A1A2, 2A1B, 2A1C1, 2A1C2, 2A2, 2A3, 2A4, 2A5, 2B, 3, 31A1, 31A2, 31B, 31C, 32A1, 32B, 33, 34, 35A1A, 35A2, 35B, 36, 37, 38, 39, 40A, 40B, 41, 42, 43, 44, 45, 46, 47A, 47B, 47C, 48A, 48B, 49, 4A1A, 4A1B, 4A2A1, 4A2A2, 4A2A3, 4A2A4, 4A2B, 4A2C1, 4A2C2, 4B1A, 4B1B, 4B2A, 5, 50, 51, 52, 53, 54, 55, 56, 57A1, 57A2, 57B1, 57B2, 57B3, 58, 59, 6B, 6C, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2334,6 +2354,11 @@
           <t>232</t>
         </is>
       </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 1A1A, 1A2, 1A3, 1A4, 1B, 1C, 1D, 1E, 1F, 1G1, 1G2, 1H, 2, 3A1A1, 3A2, 3A3, 3A4, 3A5, 3B, 3C1A1A, 3C1B, 3C1C1, 3C2, 3C3, 4A1A1A1, 4A1B, 4A2, 4A3, 4A4, 4A5, 4B, 4C, 4D, 5A1A1A, 5A1A2, 5A2, 5B, 5C1A, 5C1B1, 5C1B2, 5C2, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2341,6 +2366,11 @@
           <t>233</t>
         </is>
       </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24A, 24B, 25, 26, 27, 28, 29, 2A1A1, 2A1B, 2A2, 2B1, 2B2, 30, 31, 32, 33, 34, 36, 37, 38, 39, 3A1A1A1, 3A1A2, 3A2, 3B, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 4A1A1, 4A1A2, 4A1A3A, 4A1A3B, 4A1B1A1, 4A1B1B, 4A1B2, 4A1B3, 4A1B4, 4A1B5, 4A1B6, 4A1B7, 4A2, 4A3, 4A4, 4B1A, 4B1A1A2, 4B1B1, 4B1C1A, 4B1D, 4B2A1A, 4B2B, 50, 51A1, 51B, 52A1, 52A2, 52B, 53, 54, 55, 56, 57, 58, 59, 5A1, 5A2A, 5A2B, 5B, 5B10A, 5B10B, 5B11, 5B12, 5B13, 5B14, 5B15, 5B16, 5B17A, 5B17B, 5B18, 5B19, 5B1A, 5B2, 5B20, 5B21, 5B22, 5B23, 5B24, 5B25, 5B3A, 5B3B, 5B4, 5B5, 5B6, 5B7, 5B8A, 5B8B, 5B9, 6, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 7, 70, 71A, 71B, 72, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2348,6 +2378,11 @@
           <t>234</t>
         </is>
       </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3A, 1A3B, 1A4, 1B1A, 1B1B, 1B2, 1B3A1, 1B3A2, 1B3B, 1B3C, 2A1, 2A2, 2B1, 2B2, 2B3, 3A, 3B, 3C, 4A1, 4A2, 4B1, 4B2, 4C, 5A, 5B1, 5B2A1, 5B2A2A, 5B2A2B, 5B2A2C, 5B2B1A, 5B2B1B, 5B2B1C, 5B2B1D, 5B2B2</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2355,6 +2390,11 @@
           <t>235</t>
         </is>
       </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2362,6 +2402,11 @@
           <t>236</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1, 1A1B, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31A, 31B, 32, 33, 34, 35, 36A, 36B, 37, 38, 39, 3B1A, 3B1A2, 3B1B, 3B2, 3B3, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 4A1, 4A2A, 4A2B, 4B, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 5A, 5B, 6, 60A, 60B, 61, 62, 63, 64A, 64B, 65, 66, 67, 68, 69, 7, 70, 71, 72, 73, 74A, 74B, 75, 8, 80, 9</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2369,6 +2414,11 @@
           <t>237</t>
         </is>
       </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17A, 17B, 18, 19, 1A1A1, 1A1A1B, 1A2, 1B1, 1B2, 20, 21, 22A, 22B, 23, 24, 25, 26, 27A, 27B, 28A, 28B, 29A, 29B, 29C, 2A1A, 2A2, 2B, 30A, 30B, 31, 32, 33, 34, 35, 36, 37, 38, 39, 3A1A1, 3A1B1, 3A1B2, 3A2, 3B, 3B3A1, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 4A1A1A, 4A1A1B, 4A1A2, 4A1B, 4A1C, 4A2, 50, 51, 52, 53, 54, 55, 56, 57, 58, 5A1A, 5A1B, 5A2, 5A3, 5B1A1A, 5B2B, 5B3B, 6A1A1, 6A1B, 6A1C, 6A2, 6A3, 7, 8, 9A1A1A, 9A1A2, 9A1A3, 9A1B, 9A1C, 9A2, 9B, 9C, 9D, 9E, 9F1, 9F2, 9G</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2376,6 +2426,11 @@
           <t>238</t>
         </is>
       </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>10, 11, 12A, 12B, 13A, 13B, 14, 15, 16, 17, 18, 19, 1A, 1B, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 36, 37, 38, 39, 3A1, 3A2, 3B1A1, 40, 41, 4A, 5, 6A1A1, 6A1B, 6A1C, 6A2, 6A3, 6A4, 6A5, 6A6, 6A7, 6A8, 6A9, 6B1A, 6B1B, 6B2A1A1, 6B2B, 6B2C, 6B2D, 6B2E, 6B2F1A, 6B2F2, 6B2G, 6B2H, 6B2J1A, 7A1A1A1, 7A1A1B, 7A1B1, 7A1B2, 7A2, 7B1A, 7B1A1B, 7B1A1C, 7B1B, 7B2, 7C1A1A, 7C1B, 7C1C, 7C2A, 7C2B, 7C3, 7D1A1A1, 7D1B, 7D2, 7E, 7F1, 7F2A, 7F2B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2383,6 +2438,11 @@
           <t>239</t>
         </is>
       </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2390,6 +2450,11 @@
           <t>24</t>
         </is>
       </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1, 2A1A, 2A1B, 2A2, 2B, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2397,6 +2462,11 @@
           <t>240</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B1, 1B2, 1B3, 1C, 2, 3A, 3B, 4, 5, 6A1, 6A2, 6B, 7</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2404,6 +2474,11 @@
           <t>241</t>
         </is>
       </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>10A1A1, 10A2, 10A3, 10A4, 10B, 10C, 10D, 11A1A, 11A2, 11B, 11C, 12, 13, 14A1, 14A2, 14B, 15, 16A, 16B, 17, 18, 19, 1A, 1B, 1C1, 1C2, 2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 3, 4, 5A1, 5A2, 5A3, 5B, 6A1A, 6A2, 6B, 7A1A, 7A2, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2411,6 +2486,11 @@
           <t>242</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>10, 10A, 10B, 10C1A, 10C1B, 10C2, 10C3, 11A, 11B, 12, 13, 14, 16, 17, 19, 1A1, 1A10A, 1A11, 1A12, 1A13A1A, 1A13A1B, 1A13A2, 1A13B, 1A13C1, 1A13C2, 1A14, 1A15A, 1A16, 1A17, 1A18, 1A19, 1A1A2, 1A1B, 1A2, 1A20, 1A21A, 1A22, 1A23, 1A24, 1A25, 1A26, 1A27, 1A28, 1A29, 1A3, 1A30, 1A31, 1A4, 1A5, 1A6, 1A7, 1A8, 1A9, 1B10, 1B11, 1B12, 1B13A, 1B13B, 1B14, 1B15, 1B16, 1B17, 1B18, 1B1A1, 1B2, 1B20, 1B21, 1B22, 1B23, 1B24, 1B25, 1B26, 1B27A, 1B3, 1B4, 1B5, 1B6, 1B7, 1B8, 1B9, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 3A1A1A, 3A1A2, 3A1B1, 3A2, 3A3A, 3A3B, 3B, 3C1A, 3C2A, 3C2B, 41, 42, 4A, 4B1A1A1, 4B1B, 4B2, 4B3, 4B4, 4B5A, 4B5B, 4B6A, 4B6B, 4B7, 5A, 5B1, 5B2, 6A, 6B, 7A, 7B, 8A, 8B, 9A1, 9A2, 9B, 9C, 9D, 9E</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2418,6 +2498,11 @@
           <t>243</t>
         </is>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1, 100, 101A, 101B, 102, 103, 104, 105, 106, 107, 108A, 109, 10A1A1B, 10A1A2, 10A1B, 10A2, 10B, 110, 111, 112, 113, 11A1, 11A2, 11B1A1A, 11B1A2, 11B1B1, 11B1B2, 11B2, 12A, 12B, 13A1, 13A2, 13B, 14A, 14B, 15A, 15B, 16A1, 16A2, 16B, 17, 18A1, 18A2, 18B, 18C, 19A1A1A, 19A1A2, 19A1B, 19A2, 19B, 2, 20A, 20B, 21, 22, 23A1A, 23A1B, 23A2, 23A3, 23C, 23D, 24A1A1A1, 24A2, 24A3, 24B, 25A1, 25A2, 25B1, 25B2, 26, 27A1A1A, 27A1A2A, 27A1A2B, 27A1A2C, 27A2, 27B, 28A1, 28A2, 28B, 29A1A1, 29A1B, 29A1C, 29A1D, 29A2A, 29B1, 29B2, 3, 30A, 30A1, 30A2A, 30A2A2, 30B, 31, 31A1, 31A2, 31B1, 31B2, 32, 32A, 32B, 32C1A, 32C2, 33A1, 33A2, 33B1, 33B2, 33B3, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 46A, 46B, 47, 48, 49, 4A1A, 5, 50, 51, 52, 53, 54, 55, 60, 61, 62, 63, 64, 65, 66, 66A, 66B, 67, 68, 69, 6A1A, 6A1B, 6A1C, 6A2, 6B, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79, 7A1, 7A2, 7A3, 7B1, 7B2A1A, 7B2A1A2A, 7B2A1B, 7B2A2, 7B2B1, 7B2C, 8, 80A1A, 80A2, 80B, 81, 82, 83, 84, 85, 86, 87, 88, 89, 90, 91A, 91B, 92A1, 92A2, 92A3, 92B, 93, 94, 95, 96, 97, 98, 99, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2425,6 +2510,11 @@
           <t>244</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2432,6 +2522,11 @@
           <t>245</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1C, 1D, 1E, 1F, 1G, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2439,6 +2534,11 @@
           <t>246</t>
         </is>
       </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A, 2B1A, 2B1B, 2B1C, 2B2, 30, 31, 32, 3A1A1A, 3A1B1, 3A2, 3B1, 3B2A1A, 4A, 5A1A1A, 5A1B, 5A2, 5A3, 5B, 6, 7A1, 7A2, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2446,6 +2546,11 @@
           <t>247</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B1A1, 1B1A2, 1B1B, 1B2, 1B3, 1B4, 1B5, 1B6, 1C1A1A, 1C1A2, 1C1A3, 1C1A4, 1C1A5, 1C1A6, 1C1A7, 1C1B, 1C2, 2A1A1, 2A1A1A, 2A1A2, 2A1B, 2A2, 2B1, 2B2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2453,6 +2558,11 @@
           <t>248</t>
         </is>
       </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1A, 1B1A1, 1B1B, 1B2, 2A1, 2A2, 2B1A, 2B1B, 2B1C, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2460,6 +2570,11 @@
           <t>249</t>
         </is>
       </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B, 2C, 2D, 2E1, 2E2, 2F1, 2F2, 3A1, 3A2, 3B1, 3B2, 4A, 4B1, 4B2A1, 4B2B, 5A1, 5B, 5C, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2467,6 +2582,11 @@
           <t>25</t>
         </is>
       </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2474,6 +2594,11 @@
           <t>250</t>
         </is>
       </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2481,6 +2606,11 @@
           <t>251</t>
         </is>
       </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1B3, 1B4, 1B5, 1C, 2A1, 2A2, 2A3, 2A4, 2A5, 2A6A, 2A6B, 2A7, 2B1A, 2B1B, 2B1C, 2B1D, 2B1E, 2B1F, 2B1G, 2B1H, 2B2, 3A1, 3A2, 3B, 3C1, 3C2A1, 3C2B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2488,6 +2618,11 @@
           <t>252</t>
         </is>
       </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2495,6 +2630,11 @@
           <t>253</t>
         </is>
       </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C1, 1C2, 1C3A1, 1C3A2, 1C3B, 2A, 2B1A1A, 2B1A1B, 2B1A2, 2B1B1, 2B1C, 2B2, 3, 4A, 4B, 4C, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2502,6 +2642,11 @@
           <t>254</t>
         </is>
       </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2509,6 +2654,11 @@
           <t>255</t>
         </is>
       </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 19, 1A1, 1A2, 1A3, 1B, 1C, 1D, 1E, 1F, 1G, 1H, 1I1, 1I2, 1I3, 20, 21, 22, 23, 24, 25, 26, 27, 28, 2A1A1A, 2A1B, 2A2, 2B, 2C1A, 2C1A2, 2C1B, 2C2, 3A1A1A, 3A1A2, 3A1B, 3A2, 3B, 4A1A, 4A1B, 4A1C, 4A1D, 4A2, 4A3, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2516,6 +2666,11 @@
           <t>256</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B1A, 1B1B, 1B2, 1B3, 1B4, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A1, 2A2A1A, 2A2A2A, 2A2A2B, 2A2A3, 2A2A4A1, 2A2A4B1, 2A2A5A1A, 2A2A5C, 2A2A6A, 2A2A6B, 2A2A7, 2A2A8, 2A2B, 2A2C1, 2A2D, 2B1A, 2B1B, 2B2, 2B3A, 2B3B, 2B4, 2B5, 2B6, 2B7, 2B8, 3, 30, 31A, 31B, 32, 33, 34, 35, 36, 37, 38, 39, 40, 41, 42, 43, 44, 4A1A, 4A1B, 4A2, 4B, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2523,6 +2678,11 @@
           <t>257</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>10, 11, 12A1, 12A2, 12B, 12C, 12D1, 12D2, 13, 14, 15, 16, 17, 1A1A1A1A1, 1A1A1A2, 1A1A1B, 1A1A2, 1A1B, 1A2, 1B, 2A1A1, 2A1A2, 2A2, 2A3, 2A4A, 2A4B, 2B, 3A1A1, 3A1B, 3A2A, 3A2B, 3A3, 3B, 4A1A, 4A2, 4B, 5A1A1A, 5A1B, 5A2, 5A3, 5A4, 5B, 5B1, 5B2, 6A1A, 6A1B1, 6A1B2, 6A2, 6B1A1A, 6B1A2, 6B1B, 6B2, 7A, 7B, 7C, 7D, 7E, 7F, 7G, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2530,6 +2690,11 @@
           <t>258</t>
         </is>
       </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>10, 100, 101, 102, 103, 104, 11, 12, 13, 14, 15, 16, 17, 18, 19A, 19B, 1A1A1, 1A1A1A2, 1A1A1B, 1A1A2, 1A1B, 1A2A, 1A3A, 1A3B, 1A4, 1A5A, 1A6A1A, 1A6B, 1B1, 1B2, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A1A, 2A1B, 2A1C, 2A1D, 2A2A, 2A2B, 2B, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 3A1A1A1A1, 3A1A1A1B, 3A1A1A2, 3A1A1B, 3A1A2, 3A1B, 3A2, 3B1A1A1A, 3B1A1B, 3B1A2, 3B1B, 3B2, 3C, 40A, 40B, 41, 42, 43, 44, 45, 46, 47, 48, 49, 4A1, 4A2A, 4A2B, 4B1, 4B2A1, 50, 51, 52, 53, 54, 55, 56, 57A, 57B, 58, 59, 5A1A1A1, 5A1A1B, 5A1A2, 5A1B, 5A1C, 5A2, 5B, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 6A1A1, 6A1B, 6A2, 6A3, 6B, 70, 71, 72, 73, 74, 75, 76A, 76B, 77, 78, 79, 7A1A1A, 7A1A1B, 7A1A2A1, 7A1A2B, 7A1A2C, 7A1A3A, 7A1A3B, 7A1B, 7A1C1, 7A1C1A, 7A1C1B1A, 7A1C2, 7A1C3, 7A2A, 7A2B, 7A3, 7B1A, 7B1B, 7B2, 7C1A1, 7C1A2, 7C1B1, 7C1B2, 7C2A, 7C2B, 8, 80, 81, 82, 83, 84, 85, 86, 87, 88, 89, 9, 90, 91, 92, 93, 94, 95, 96, 97, 98, 99</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2537,6 +2702,11 @@
           <t>259</t>
         </is>
       </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>1A1, 1B, 2A1</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2544,6 +2714,11 @@
           <t>26</t>
         </is>
       </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2551,6 +2726,11 @@
           <t>260</t>
         </is>
       </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1A1A1A, 1A1A1A1A2, 1A1A1A1B, 1A1A1A1C, 1A1A1A2, 1A1A1B, 1A1A2, 1A1A3, 1A1B, 1A1C1, 1A2, 1B1A1A, 1B1A1B1, 1B1A2, 1B1B, 1B2, 1B3, 20, 27, 28, 29, 2A1A1A, 2A1B, 2A2, 2A3, 2B, 3, 30, 31, 32A, 32B, 33, 34, 35, 36A, 36B, 37, 38, 39A, 39B, 4, 40, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2558,6 +2738,11 @@
           <t>261</t>
         </is>
       </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 1A1A, 1A1A1, 1A1B, 1A2, 1B, 2A1A1A, 2A1A2A, 2A1B, 2A2, 2B1A1A1, 2B1A2, 2B1A3, 2B1B, 2B2, 2C1A1, 2C1A2, 2C1B, 2C2, 2C3A, 2C3B, 3A1A, 3B, 4A, 4B1, 4B2, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2565,6 +2750,11 @@
           <t>262</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>10, 11, 113, 12, 14, 15, 16, 17, 18, 1A1A1A1A, 1A1A2, 1A1B, 1A2, 1A3, 1B, 2, 2A1A1, 2A1A2, 2A1A3, 2A1B, 2A2, 2A3, 2A4, 2B, 3A1, 3A2A, 3A2B, 3A2C, 3A2D, 3A2E, 3A2F, 3B, 3C1A, 3D1, 3D2, 4A1, 4A2A, 4A2B, 4A2C, 4A3, 4B, 5A1, 5A2A, 5B1A, 5C1, 5C2, 5C3, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2572,6 +2762,11 @@
           <t>263</t>
         </is>
       </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1B, 2A, 2B, 2C, 2D, 2E</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2579,6 +2774,11 @@
           <t>264</t>
         </is>
       </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2586,6 +2786,11 @@
           <t>265</t>
         </is>
       </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B, 2C, 3A, 3B, 4A1, 4A2, 4B, 4C, 4D, 5A, 5B</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2593,6 +2798,11 @@
           <t>266</t>
         </is>
       </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1B, 1A1C, 1A2, 1B1, 1B2, 2A1, 2A2, 2B1, 2B2</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2600,6 +2810,11 @@
           <t>267</t>
         </is>
       </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2607,6 +2822,11 @@
           <t>268</t>
         </is>
       </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A1A, 2A1B, 2A2A, 2A2B, 2B, 3A1A, 3A1B, 3A2, 3B1, 3B2, 3C, 4A, 4B, 5A, 5B, 5C, 6A1, 6A2, 6B1, 6B2, 6C, 7A1, 7A2, 7B, 8A12, 8A1A, 8A2, 8B1, 8B2, 8B3</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2614,6 +2834,11 @@
           <t>269</t>
         </is>
       </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B2, 2C1A, 2C1B, 2C1C, 2C2, 2D, 2E, 3A1A, 3A1B, 3A2, 3B1A, 3B1B, 3B2, 3B3, 3C1A, 3C1B, 3C2</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2621,6 +2846,11 @@
           <t>27</t>
         </is>
       </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A, 3B, 3C</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2628,6 +2858,11 @@
           <t>270</t>
         </is>
       </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1B3, 2, 3A, 3B, 4A, 4B, 4C</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2635,6 +2870,11 @@
           <t>271</t>
         </is>
       </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 19, 1A1A, 1B, 1C1A1, 1C1A1A2, 1C1A1B, 1C2A, 1C2B, 1D1A1A, 1D1A2, 1D1B, 1E, 1F, 1G, 1H, 1I1, 1I2, 1J1A1, 1J1A1B, 1J1A2, 1J1B, 1J2, 1K1A1, 1K1B, 1K2, 1K3, 1L, 1M1A1A, 1M1B, 1M2, 1N1A, 1N1B, 1N2, 1O, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 2H1, 2H2, 2I, 2J1, 2J2, 2K, 2L, 2M, 2N, 2O, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 3A1, 3A2, 3B1, 3B2, 3C, 3D, 3E, 3F, 3G1A, 3G2A, 3G2B, 3G2C, 3G3, 3G4, 3H, 3I, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 4A1, 4A2, 4A3, 4A4, 4A5, 4B1, 4B2, 4B3, 4B4, 5A, 5B, 5C, 6A, 6B, 7A, 7B1A1, 7C, 8A, 8B1, 8B2, 8C1, 8C2, 9</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2642,6 +2882,11 @@
           <t>272</t>
         </is>
       </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>1, 16, 17, 18, 19, 20, 21, 2A1A1, 2A1B, 2A2, 2A3, 2B1A1A1A1, 2B2A, 2B2B, 2B2C, 2B2D, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2649,6 +2894,11 @@
           <t>273</t>
         </is>
       </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>1A1A1, 1A1B, 1A1C, 1B, 2A2A, 2A2B, 2B, 3A1, 3A2, 3A3, 3A4, 3B, 3C, 4A, 4B, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -2656,6 +2906,11 @@
           <t>274</t>
         </is>
       </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A, 1B1, 1B2, 1B3A1, 1B3B, 1B3C, 20, 21, 2A1A1, 2A2, 2B1A, 2B1B1, 2B1C, 2B2A1, 2B2B, 2B2C, 2B2D, 3, 4, 5, 6A1A, 6A1B, 6A1C, 6A1D, 6A2, 6B, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -2663,6 +2918,11 @@
           <t>275/A</t>
         </is>
       </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -2670,6 +2930,11 @@
           <t>275/B</t>
         </is>
       </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -2677,6 +2942,11 @@
           <t>276</t>
         </is>
       </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -2684,6 +2954,11 @@
           <t>277/A</t>
         </is>
       </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -2691,6 +2966,11 @@
           <t>277/B</t>
         </is>
       </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -2698,6 +2978,11 @@
           <t>278/A</t>
         </is>
       </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -2705,6 +2990,11 @@
           <t>278/B</t>
         </is>
       </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -2712,6 +3002,11 @@
           <t>278/C</t>
         </is>
       </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -2719,6 +3014,11 @@
           <t>279</t>
         </is>
       </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2A, 2A2B, 2A3A, 2A3B, 2A4, 2B1, 2B2</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -2726,6 +3026,11 @@
           <t>28</t>
         </is>
       </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -2733,6 +3038,11 @@
           <t>280</t>
         </is>
       </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1, 1A2, 1B, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A1, 2A2, 2B, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 3A1A, 3A1A2, 3A2A1, 3A2B, 3B1A1A, 3B2, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 4A1, 4A2, 4A3, 4B, 5, 50, 51, 52, 53, 54, 55, 56, 57, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -2740,6 +3050,11 @@
           <t>281</t>
         </is>
       </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>11C2A, 1A1A1, 1A1B, 1A1C, 1A2, 1A3, 1B, 1C1, 1C2B, 1C2C, 1C2D, 1C3, 2A, 2B1, 2B2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -2747,6 +3062,11 @@
           <t>282</t>
         </is>
       </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>10, 11A, 11B, 12, 13, 14, 15, 16, 17, 18, 19, 1A1, 1A2, 1A3A, 1A3A1, 1A3A1A1A1B, 1A3A1A1A2, 1A3A1A1B1, 1A3A1A2, 1A3A1B, 1A3A1C, 1A3A1D, 1A3A1E, 1A3A1F, 1A3A2, 1A3B1, 1B, 1C, 1D, 1E, 1F, 1G, 20A, 20B, 21A, 21B, 22, 23, 24, 25A, 25B, 26, 27, 28, 29, 3A1A, 3A1A1A2, 3A1A1B, 3A1A1C, 3A1A2, 3A1B, 3A2, 3B, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 4A1A1, 4A1A1B, 4A1A2, 4A1A3, 4A1B1, 4A1C, 4A2A, 50, 51, 52, 53, 54, 55, 56A, 56B, 57, 58A, 58B, 59, 61, 62A, 62B, 63, 64, 65, 66, 67, 68, 69, 6A1A1, 6A1B, 6A2, 6A3A, 6A3B, 6A3C, 6B, 7A1A1, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -2754,6 +3074,11 @@
           <t>283</t>
         </is>
       </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1B, 1A1C, 1A2, 1B, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -2761,6 +3086,11 @@
           <t>284</t>
         </is>
       </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1B, 1C, 2</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -2768,6 +3098,11 @@
           <t>285</t>
         </is>
       </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -2775,6 +3110,11 @@
           <t>286/A</t>
         </is>
       </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -2782,6 +3122,11 @@
           <t>286/B</t>
         </is>
       </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -2789,6 +3134,11 @@
           <t>287</t>
         </is>
       </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -2796,6 +3146,11 @@
           <t>288</t>
         </is>
       </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -2803,6 +3158,11 @@
           <t>289/A</t>
         </is>
       </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -2810,6 +3170,11 @@
           <t>289/B</t>
         </is>
       </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -2817,6 +3182,11 @@
           <t>29</t>
         </is>
       </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1C, 2, 3A, 3B1A, 3B2, 3B3, 3C1A, 3C1B, 3C2</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -2824,6 +3194,11 @@
           <t>290</t>
         </is>
       </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B1A, 2B1B, 2B1C, 2B2, 2C1A, 2C1B, 2C2, 3A1, 3A2, 3B1A1A1, 3B1A2, 3B1B, 3B1C, 3B2, 3B3, 3B4, 3C, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -2831,6 +3206,11 @@
           <t>291/A</t>
         </is>
       </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -2838,6 +3218,11 @@
           <t>291/B</t>
         </is>
       </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -2845,6 +3230,11 @@
           <t>292</t>
         </is>
       </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -2852,6 +3242,11 @@
           <t>293</t>
         </is>
       </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -2859,6 +3254,11 @@
           <t>294</t>
         </is>
       </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -2866,6 +3266,11 @@
           <t>295</t>
         </is>
       </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B1, 4B2</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -2873,6 +3278,11 @@
           <t>296</t>
         </is>
       </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2A, 2B, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -2880,6 +3290,11 @@
           <t>297</t>
         </is>
       </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -2887,11 +3302,21 @@
           <t>298</t>
         </is>
       </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
           <t>299</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>1, 2</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Pethikuppam_13.433004_80.120213.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Pethikuppam_13.433004_80.120213.xlsx
@@ -3326,6 +3326,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 2A1, 2A2, 2A3A, 2A3B, 2B1, 2B2</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -3333,6 +3338,11 @@
           <t>30</t>
         </is>
       </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -3340,6 +3350,11 @@
           <t>300</t>
         </is>
       </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -3347,6 +3362,11 @@
           <t>301</t>
         </is>
       </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -3354,6 +3374,11 @@
           <t>302</t>
         </is>
       </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -3361,6 +3386,11 @@
           <t>303</t>
         </is>
       </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -3368,6 +3398,11 @@
           <t>304</t>
         </is>
       </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -3375,6 +3410,11 @@
           <t>305</t>
         </is>
       </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -3382,6 +3422,11 @@
           <t>306</t>
         </is>
       </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B2</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -3389,6 +3434,11 @@
           <t>307</t>
         </is>
       </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A2, 2B1B, 2B2B</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -3396,6 +3446,11 @@
           <t>308</t>
         </is>
       </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -3403,6 +3458,11 @@
           <t>309</t>
         </is>
       </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -3410,6 +3470,11 @@
           <t>31</t>
         </is>
       </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -3417,6 +3482,11 @@
           <t>310</t>
         </is>
       </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>12, 13, 1A1, 1A2, 1B1A, 1B1B, 1B1C, 1B2, 1C, 1D, 1E, 1F, 2</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -3424,6 +3494,11 @@
           <t>311</t>
         </is>
       </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2B2</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -3431,6 +3506,11 @@
           <t>312</t>
         </is>
       </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -3438,6 +3518,11 @@
           <t>313</t>
         </is>
       </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -3445,6 +3530,11 @@
           <t>314</t>
         </is>
       </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>1A, 1B</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -3452,6 +3542,11 @@
           <t>315</t>
         </is>
       </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -3459,6 +3554,11 @@
           <t>316</t>
         </is>
       </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -3466,6 +3566,11 @@
           <t>317</t>
         </is>
       </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -3473,6 +3578,11 @@
           <t>318</t>
         </is>
       </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -3480,6 +3590,11 @@
           <t>319</t>
         </is>
       </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -3487,6 +3602,11 @@
           <t>32</t>
         </is>
       </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1C, 2, 3A1, 3A2A, 3A2B, 3A3, 3A4, 3B1A1, 3B1B, 3B1C, 3B2, 3C1, 3C2</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -3494,6 +3614,11 @@
           <t>320</t>
         </is>
       </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -3501,6 +3626,11 @@
           <t>321</t>
         </is>
       </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -3508,6 +3638,11 @@
           <t>322</t>
         </is>
       </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -3515,6 +3650,11 @@
           <t>323</t>
         </is>
       </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -3522,6 +3662,11 @@
           <t>324</t>
         </is>
       </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -3529,6 +3674,11 @@
           <t>325</t>
         </is>
       </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -3536,6 +3686,11 @@
           <t>326</t>
         </is>
       </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -3543,6 +3698,11 @@
           <t>327</t>
         </is>
       </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -3550,6 +3710,11 @@
           <t>328</t>
         </is>
       </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -3557,6 +3722,11 @@
           <t>329</t>
         </is>
       </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -3564,6 +3734,11 @@
           <t>33</t>
         </is>
       </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B1, 4B2, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -3571,6 +3746,11 @@
           <t>330</t>
         </is>
       </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -3578,6 +3758,11 @@
           <t>331</t>
         </is>
       </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -3585,11 +3770,21 @@
           <t>332</t>
         </is>
       </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
           <t>333</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Pethikuppam_13.433004_80.120213.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Pethikuppam_13.433004_80.120213.xlsx
@@ -3794,6 +3794,11 @@
           <t>334</t>
         </is>
       </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -3801,6 +3806,11 @@
           <t>335</t>
         </is>
       </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -3808,6 +3818,11 @@
           <t>337</t>
         </is>
       </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -3815,6 +3830,11 @@
           <t>338</t>
         </is>
       </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -3822,6 +3842,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -3829,6 +3854,11 @@
           <t>35</t>
         </is>
       </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2A3A, 2A3B, 2A4, 2A5, 2A6, 2B1, 2B2</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -3836,6 +3866,11 @@
           <t>36</t>
         </is>
       </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -3843,6 +3878,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -3850,6 +3890,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -3857,6 +3902,11 @@
           <t>39</t>
         </is>
       </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -3864,6 +3914,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -3871,6 +3926,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -3878,6 +3938,11 @@
           <t>41</t>
         </is>
       </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -3885,6 +3950,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -3892,6 +3962,11 @@
           <t>43</t>
         </is>
       </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C, 1D, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -3899,6 +3974,11 @@
           <t>44</t>
         </is>
       </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -3906,6 +3986,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -3913,6 +3998,11 @@
           <t>46</t>
         </is>
       </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -3920,6 +4010,11 @@
           <t>47</t>
         </is>
       </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -3927,6 +4022,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 5A, 5B1, 5B2</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -3934,6 +4034,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -3941,6 +4046,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A, 3B, 4, 5A1, 5A2, 5A3, 5B, 6, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -3948,6 +4058,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -3955,6 +4070,11 @@
           <t>51</t>
         </is>
       </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -3962,6 +4082,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -3969,6 +4094,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -3976,6 +4106,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -3983,6 +4118,11 @@
           <t>55</t>
         </is>
       </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D1, 1D2A, 1D2B, 2A1, 2A2, 2B1, 2B2, 2C1, 2C2, 3A, 3B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -3990,6 +4130,11 @@
           <t>56</t>
         </is>
       </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -3997,6 +4142,11 @@
           <t>57</t>
         </is>
       </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -4004,6 +4154,11 @@
           <t>58/A</t>
         </is>
       </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -4011,6 +4166,11 @@
           <t>58/B</t>
         </is>
       </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -4018,6 +4178,11 @@
           <t>59</t>
         </is>
       </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -4025,6 +4190,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -4032,6 +4202,11 @@
           <t>60</t>
         </is>
       </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -4039,6 +4214,11 @@
           <t>61</t>
         </is>
       </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -4046,6 +4226,11 @@
           <t>62</t>
         </is>
       </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1A4, 1A5A, 1A5B, 1B, 2, 3A1, 3A2, 3A3, 3B, 4A, 4B, 4C, 5A1, 5A2, 5A3, 5B</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -4053,6 +4238,11 @@
           <t>63</t>
         </is>
       </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -4060,6 +4250,11 @@
           <t>64</t>
         </is>
       </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>10, 100, 101, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A10, 1A11, 1A12, 1A13, 1A1A1A, 1A2, 1A3, 1A4, 1A5, 1A6, 1A7, 1A8, 1A9, 1B1A1, 1B2, 1B3, 1B4, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A1A, 2A1B, 2A1C, 2A2, 2A3, 2B, 30, 31, 32, 33, 34, 35, 36, 37, 38A, 38B, 39, 3A1, 3A2, 3A3, 3B1B1, 3B2, 3B3, 3B4, 3B5A, 3B5B, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 5, 50, 51, 52, 53, 54, 55, 56, 57, 58, 59, 6, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 7, 70, 71, 72, 73, 74, 75, 76, 77, 78, 79, 8, 80, 81, 82, 83, 84, 85, 86, 87, 88, 89, 9, 90, 91, 92, 93, 94, 95, 96, 97, 98, 99</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -4067,6 +4262,11 @@
           <t>65</t>
         </is>
       </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B1, 1B2, 1B3, 1B4, 1B5, 2A, 2B, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -4074,6 +4274,11 @@
           <t>66</t>
         </is>
       </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -4081,6 +4286,11 @@
           <t>67</t>
         </is>
       </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A2A, 1C, 2A1A, 2A1B, 2A1C, 2A2, 2B, 2C1, 2C2</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -4088,6 +4298,11 @@
           <t>68</t>
         </is>
       </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -4095,6 +4310,11 @@
           <t>69</t>
         </is>
       </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1B, 1A2A, 1A2B, 1A3A1A, 1A3A2, 1A3B1, 1A3B2, 1B1, 1B2, 1C1, 1C2, 2A1, 2A2, 2B1A, 2B1B, 2B2, 3A1A, 3A1B, 3A2A1, 3A2A2, 3A2B1, 3A2B2, 3B1, 3B2, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -4102,6 +4322,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>10, 11, 1A1A1, 1A1B, 1A2A1, 1A2B, 1A3, 1B, 1C, 1D, 1E, 2A1, 2A2, 2B, 2C, 3A, 3B, 4A1A1, 4A2, 4A3, 4B1, 4B2, 4B3, 4B4, 5A1A, 5A2A, 5A2B, 5A2C, 5A3, 5B, 5C, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -4109,6 +4334,11 @@
           <t>70</t>
         </is>
       </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -4116,6 +4346,11 @@
           <t>71</t>
         </is>
       </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>1A, 1B, 3, 4A, 4B, 5A, 5B, 6</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -4123,6 +4358,11 @@
           <t>72</t>
         </is>
       </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -4130,6 +4370,11 @@
           <t>73</t>
         </is>
       </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -4137,6 +4382,11 @@
           <t>74</t>
         </is>
       </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -4144,6 +4394,11 @@
           <t>75</t>
         </is>
       </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>17, 1A, 1B, 1C, 1D, 1E, 1G1, 1G2, 1G3, 1H, 1I, 1J, 1K, 1L, 1M, 1N, 1O, 1P, 1R, 1S, 1T, 1U, 2A1, 2A2, 2B, 3A, 3B, 3C, 4A1, 4A2, 4A3, 4B, 6</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -4151,6 +4406,11 @@
           <t>76</t>
         </is>
       </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -4158,6 +4418,11 @@
           <t>77</t>
         </is>
       </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1B3, 1B4, 1B5, 1B6, 1B7, 2</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -4165,6 +4430,11 @@
           <t>78</t>
         </is>
       </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B1, 2B2</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -4172,6 +4442,11 @@
           <t>79</t>
         </is>
       </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -4179,6 +4454,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2, 3, 4A1, 4A2, 4A3, 4B1, 4B2, 4C</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -4186,6 +4466,11 @@
           <t>80</t>
         </is>
       </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -4193,6 +4478,11 @@
           <t>81</t>
         </is>
       </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1B, 1A2A, 1A2B, 1A3, 1B1, 1B2, 1C1, 1C2, 1C3, 1C4, 1C5, 2, 3A1, 3A2, 3B1A, 3B1A2, 3B1A3, 3B1A4, 3B1A5, 3B2, 3C1A, 3C1B, 3C2, 3D1A, 3D1B, 3D1C, 3D1D, 3D1E, 3D2, 3E, 4A, 4B, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -4200,6 +4490,11 @@
           <t>82/A</t>
         </is>
       </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -4207,6 +4502,11 @@
           <t>82/B</t>
         </is>
       </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -4214,6 +4514,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1, 2B2, 3A1, 3A2, 3B, 3C</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -4221,6 +4526,11 @@
           <t>84</t>
         </is>
       </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12A, 12B, 13, 14A, 14B, 15, 16, 17, 18, 19, 20A, 20B, 21A, 21B, 22A, 22B, 23, 24, 25, 26, 27, 28, 29, 2A1A1, 2A1B, 2A1C, 2A3, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 4, 40, 41, 42, 43, 44, 45, 46, 47, 48, 49, 5, 50, 51, 57, 58, 59, 6, 60, 61, 62, 63, 64, 65, 66, 67, 68, 69, 7, 70A, 70B, 71, 72, 73, 74, 75, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -4228,6 +4538,11 @@
           <t>85</t>
         </is>
       </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B1A, 2B1B, 2B2</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -4235,6 +4550,11 @@
           <t>86</t>
         </is>
       </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -4242,6 +4562,11 @@
           <t>87/A</t>
         </is>
       </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -4249,11 +4574,21 @@
           <t>87/B</t>
         </is>
       </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
           <t>88</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Pethikuppam_13.433004_80.120213.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Pethikuppam_13.433004_80.120213.xlsx
@@ -4598,6 +4598,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -4605,6 +4610,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -4612,6 +4622,11 @@
           <t>90</t>
         </is>
       </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C1, 1D1, 1D2A, 1D2B, 2A, 2B, 2C1, 2C2, 3A1, 3A2A, 3A2B1, 3A2B2, 3B, 3C1, 3C2A, 3C2B, 3C3A, 3C3B, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -4619,6 +4634,11 @@
           <t>91</t>
         </is>
       </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -4626,6 +4646,11 @@
           <t>92</t>
         </is>
       </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -4633,6 +4658,11 @@
           <t>93</t>
         </is>
       </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>1A1A, 1A2A, 1A2B, 1B1, 1B2, 2A, 2B, 4A, 4B1A, 4B2, 4B3</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -4640,6 +4670,11 @@
           <t>94</t>
         </is>
       </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -4647,6 +4682,11 @@
           <t>95</t>
         </is>
       </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -4654,6 +4694,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11A, 11B, 12A, 12B, 13A, 13B, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 2A1A1, 2A1B, 2A1C, 2A2, 2A3, 2A4, 2B1A, 2B1B, 2B1C, 2B2, 3A, 3B, 3C1, 3C2, 4, 5A, 5B, 6A1A1A, 6A1A2, 6A1B, 6A2, 6A3, 6B, 6C, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -4661,6 +4706,11 @@
           <t>97</t>
         </is>
       </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 1A1A1A, 1A2, 1B, 1C, 1D, 2A1A1A, 2A1B, 2A2, 2B, 3, 4A, 4B, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -4668,11 +4718,21 @@
           <t>98</t>
         </is>
       </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>1, 2A1A1A, 2A1B, 2A2, 2A3, 2A4, 2B, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
           <t>99</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A1, 3A2A, 3A3, 3B, 4A1A, 4A1B, 4A2, 4A3, 4B</t>
         </is>
       </c>
     </row>
